--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -3899,7 +3899,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>동양생명</t>
+          <t>동양생명보험</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5456,7 +5456,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>세아메카닉스</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>퀀텀레일</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>아이로보틱스</t>
+          <t>금강제강</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>퀀텀레일</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -23136,7 +23136,7 @@
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>나무에이엑스</t>
+          <t>나무AX</t>
         </is>
       </c>
       <c r="B1218" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>금강제강</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>퀀텀레일</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>코윈테크</t>
+          <t>코윈로보틱스</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -22592,7 +22592,7 @@
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>경인전자</t>
+          <t>케이아이이</t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>아이로보틱스</t>
+          <t>금강제강</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>금강제강</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -34511,7 +34511,7 @@
     <row r="1889">
       <c r="A1889" t="inlineStr">
         <is>
-          <t>케이카</t>
+          <t>KG모빌리티플랫폼</t>
         </is>
       </c>
       <c r="B1889" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>퀀텀레일</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>아이로보틱스</t>
+          <t>금강제강</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -2805,7 +2805,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>국일제지</t>
+          <t>에스엠국일</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>퀀텀레일</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -18953,7 +18953,7 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>캔버스엔</t>
+          <t>빅텐츠</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
@@ -19523,7 +19523,7 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>엔키AX</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>금강제강</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -2038,7 +2038,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S&amp;K폴리텍</t>
+          <t>S&amp;K글로벌</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>동아쏘시오홀딩스</t>
+          <t>동아제약</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>퀀텀레일</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -25716,7 +25716,7 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>만호제강</t>
+          <t>MH머트리얼즈</t>
         </is>
       </c>
       <c r="B1370" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>아이로보틱스</t>
+          <t>금강제강</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">
